--- a/Excel_export/2025T136_heating120.xlsx
+++ b/Excel_export/2025T136_heating120.xlsx
@@ -989,16 +989,16 @@
     <t>UTC timestamp in ISO 8601 format</t>
   </si>
   <si>
-    <t>Raw GPS latitude from NetCDF temperature axis; interpolated to heating axes when needed</t>
+    <t>Raw GPS latitude on this data time axis</t>
   </si>
   <si>
-    <t>Raw GPS longitude from NetCDF temperature axis; interpolated to heating axes when needed</t>
+    <t>Raw GPS longitude on this data time axis</t>
   </si>
   <si>
-    <t>Quality-controlled latitude; interpolated to heating axes when needed</t>
+    <t>Quality-controlled latitude on this data time axis</t>
   </si>
   <si>
-    <t>Quality-controlled longitude; interpolated to heating axes when needed</t>
+    <t>Quality-controlled longitude on this data time axis</t>
   </si>
   <si>
     <t>1=original; 2=interpolated; 3=invalid; 4=edge extrapolated; 5=long-gap filled</t>
@@ -2173,10 +2173,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>83.858400000000003</v>
+        <v>83.866100000000003</v>
       </c>
       <c r="C2" s="0">
-        <v>-12.4909</v>
+        <v>-12.164999999999999</v>
       </c>
       <c r="D2" s="0">
         <v>83.858500000000006</v>
@@ -2930,10 +2930,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>83.842500000000001</v>
+        <v>83.808000000000007</v>
       </c>
       <c r="C3" s="0">
-        <v>-13.144500000000001</v>
+        <v>-13.0693</v>
       </c>
       <c r="D3" s="0">
         <v>83.842600000000004</v>
@@ -3687,10 +3687,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>83.765299999999996</v>
+        <v>83.791499999999999</v>
       </c>
       <c r="C4" s="0">
-        <v>-13.3164</v>
+        <v>-13.7148</v>
       </c>
       <c r="D4" s="0">
         <v>83.791499999999999</v>
@@ -4444,10 +4444,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>83.791399999999996</v>
+        <v>83.799800000000005</v>
       </c>
       <c r="C5" s="0">
-        <v>-13.715199999999999</v>
+        <v>-13.3925</v>
       </c>
       <c r="D5" s="0">
         <v>83.791399999999996</v>
@@ -5201,10 +5201,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>83.710999999999999</v>
+        <v>83.705100000000002</v>
       </c>
       <c r="C6" s="0">
-        <v>-13.8246</v>
+        <v>-14.194699999999999</v>
       </c>
       <c r="D6" s="0">
         <v>83.7136</v>
@@ -5958,10 +5958,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>83.334400000000002</v>
+        <v>83.355400000000003</v>
       </c>
       <c r="C7" s="0">
-        <v>-13.4213</v>
+        <v>-13.435499999999999</v>
       </c>
       <c r="D7" s="0">
         <v>83.334400000000002</v>
@@ -6715,10 +6715,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>82.784199999999998</v>
+        <v>82.776499999999999</v>
       </c>
       <c r="C8" s="0">
-        <v>-12.6526</v>
+        <v>-12.9306</v>
       </c>
       <c r="D8" s="0">
         <v>82.784199999999998</v>
@@ -7472,10 +7472,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>82.632999999999996</v>
+        <v>82.641000000000005</v>
       </c>
       <c r="C9" s="0">
-        <v>-12.6785</v>
+        <v>-12.407400000000001</v>
       </c>
       <c r="D9" s="0">
         <v>82.632999999999996</v>
@@ -8229,10 +8229,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>82.509200000000007</v>
+        <v>82.474800000000002</v>
       </c>
       <c r="C10" s="0">
-        <v>-11.9009</v>
+        <v>-11.846399999999999</v>
       </c>
       <c r="D10" s="0">
         <v>82.509399999999999</v>
@@ -9746,7 +9746,7 @@
         <v>82.288200000000003</v>
       </c>
       <c r="C12" s="0">
-        <v>-6.9581</v>
+        <v>-6.9593999999999996</v>
       </c>
       <c r="D12" s="0">
         <v>82.288200000000003</v>
@@ -10500,10 +10500,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>82.450199999999995</v>
+        <v>82.450100000000006</v>
       </c>
       <c r="C13" s="0">
-        <v>-6.0065999999999997</v>
+        <v>-6.0090000000000003</v>
       </c>
       <c r="D13" s="0">
         <v>82.450100000000006</v>
@@ -11260,7 +11260,7 @@
         <v>82.431200000000004</v>
       </c>
       <c r="C14" s="0">
-        <v>-4.6268000000000002</v>
+        <v>-4.6280999999999999</v>
       </c>
       <c r="D14" s="0">
         <v>82.433999999999997</v>
@@ -12771,10 +12771,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>82.259399999999999</v>
+        <v>82.261399999999995</v>
       </c>
       <c r="C16" s="0">
-        <v>-3.4582000000000002</v>
+        <v>-3.1945999999999999</v>
       </c>
       <c r="D16" s="0">
         <v>82.259399999999999</v>
@@ -13528,10 +13528,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>82.377899999999997</v>
+        <v>82.377799999999993</v>
       </c>
       <c r="C17" s="0">
-        <v>-2.4300000000000002</v>
+        <v>-2.4308999999999998</v>
       </c>
       <c r="D17" s="0">
         <v>82.377899999999997</v>
@@ -14288,7 +14288,7 @@
         <v>82.453500000000005</v>
       </c>
       <c r="C18" s="0">
-        <v>-1.3619000000000001</v>
+        <v>-1.3638999999999999</v>
       </c>
       <c r="D18" s="0">
         <v>82.453500000000005</v>
@@ -15042,10 +15042,10 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>82.526200000000003</v>
+        <v>82.490399999999994</v>
       </c>
       <c r="C19" s="0">
-        <v>-0.55089999999999995</v>
+        <v>-0.82240000000000002</v>
       </c>
       <c r="D19" s="0">
         <v>82.491100000000003</v>
@@ -15799,10 +15799,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>82.526799999999994</v>
+        <v>82.526700000000005</v>
       </c>
       <c r="C20" s="0">
-        <v>0.00089999999999999998</v>
+        <v>0</v>
       </c>
       <c r="D20" s="0">
         <v>82.526600000000002</v>
@@ -16556,10 +16556,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>82.526300000000006</v>
+        <v>82.561400000000006</v>
       </c>
       <c r="C21" s="0">
-        <v>0.55300000000000005</v>
+        <v>0.83030000000000004</v>
       </c>
       <c r="D21" s="0">
         <v>82.526300000000006</v>
@@ -17313,10 +17313,10 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>82.561899999999994</v>
+        <v>82.561400000000006</v>
       </c>
       <c r="C22" s="0">
-        <v>0.55459999999999998</v>
+        <v>0.83030000000000004</v>
       </c>
       <c r="D22" s="0">
         <v>82.561400000000006</v>
@@ -18070,10 +18070,10 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>82.596900000000005</v>
+        <v>82.561899999999994</v>
       </c>
       <c r="C23" s="0">
-        <v>0.83440000000000003</v>
+        <v>0.55359999999999998</v>
       </c>
       <c r="D23" s="0">
         <v>82.596900000000005</v>
@@ -18827,10 +18827,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>82.632599999999996</v>
+        <v>82.631900000000002</v>
       </c>
       <c r="C24" s="0">
-        <v>0.83840000000000003</v>
+        <v>1.1177999999999999</v>
       </c>
       <c r="D24" s="0">
         <v>82.633099999999999</v>
@@ -19587,7 +19587,7 @@
         <v>82.671999999999997</v>
       </c>
       <c r="C25" s="0">
-        <v>1.1244000000000001</v>
+        <v>1.1233</v>
       </c>
       <c r="D25" s="0">
         <v>82.671999999999997</v>
@@ -20341,10 +20341,10 @@
         <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>82.704599999999999</v>
+        <v>82.705799999999996</v>
       </c>
       <c r="C26" s="0">
-        <v>1.9749000000000001</v>
+        <v>1.6930000000000001</v>
       </c>
       <c r="D26" s="0">
         <v>82.704599999999999</v>
@@ -21098,10 +21098,10 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>82.700000000000003</v>
+        <v>82.700199999999995</v>
       </c>
       <c r="C27" s="0">
-        <v>2.8220999999999998</v>
+        <v>2.8201999999999998</v>
       </c>
       <c r="D27" s="0">
         <v>82.700100000000006</v>
@@ -21855,10 +21855,10 @@
         <v>27</v>
       </c>
       <c r="B28" s="0">
-        <v>82.659800000000004</v>
+        <v>82.624600000000001</v>
       </c>
       <c r="C28" s="0">
-        <v>2.8052000000000001</v>
+        <v>2.7927</v>
       </c>
       <c r="D28" s="0">
         <v>82.658199999999994</v>
@@ -22615,7 +22615,7 @@
         <v>82.587299999999999</v>
       </c>
       <c r="C29" s="0">
-        <v>3.0556000000000001</v>
+        <v>3.0566</v>
       </c>
       <c r="D29" s="0">
         <v>82.587299999999999</v>
@@ -23369,10 +23369,10 @@
         <v>29</v>
       </c>
       <c r="B30" s="0">
-        <v>82.551400000000001</v>
+        <v>82.516300000000001</v>
       </c>
       <c r="C30" s="0">
-        <v>3.0448</v>
+        <v>3.0272999999999999</v>
       </c>
       <c r="D30" s="0">
         <v>82.549800000000005</v>
@@ -24126,10 +24126,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="0">
-        <v>82.447000000000003</v>
+        <v>82.411699999999996</v>
       </c>
       <c r="C31" s="0">
-        <v>2.7263000000000002</v>
+        <v>2.7134</v>
       </c>
       <c r="D31" s="0">
         <v>82.445300000000003</v>
@@ -24883,10 +24883,10 @@
         <v>31</v>
       </c>
       <c r="B32" s="0">
-        <v>82.335899999999995</v>
+        <v>82.335999999999999</v>
       </c>
       <c r="C32" s="0">
-        <v>2.6879</v>
+        <v>2.6880000000000002</v>
       </c>
       <c r="D32" s="0">
         <v>82.335899999999995</v>
@@ -25640,10 +25640,10 @@
         <v>32</v>
       </c>
       <c r="B33" s="0">
-        <v>82.196799999999996</v>
+        <v>82.198300000000003</v>
       </c>
       <c r="C33" s="0">
-        <v>2.1131000000000002</v>
+        <v>1.8475999999999999</v>
       </c>
       <c r="D33" s="0">
         <v>82.196799999999996</v>
@@ -26397,10 +26397,10 @@
         <v>33</v>
       </c>
       <c r="B34" s="0">
-        <v>82.049999999999997</v>
+        <v>82.014799999999994</v>
       </c>
       <c r="C34" s="0">
-        <v>2.0731000000000002</v>
+        <v>2.0638000000000001</v>
       </c>
       <c r="D34" s="0">
         <v>82.049999999999997</v>
@@ -27154,10 +27154,10 @@
         <v>34</v>
       </c>
       <c r="B35" s="0">
-        <v>81.9392</v>
+        <v>81.903999999999996</v>
       </c>
       <c r="C35" s="0">
-        <v>2.8121999999999998</v>
+        <v>2.7989000000000002</v>
       </c>
       <c r="D35" s="0">
         <v>81.9392</v>
@@ -27911,10 +27911,10 @@
         <v>35</v>
       </c>
       <c r="B36" s="0">
-        <v>81.719499999999996</v>
+        <v>81.719999999999999</v>
       </c>
       <c r="C36" s="0">
-        <v>2.9900000000000002</v>
+        <v>2.9866000000000001</v>
       </c>
       <c r="D36" s="0">
         <v>81.719800000000006</v>
@@ -28668,10 +28668,10 @@
         <v>36</v>
       </c>
       <c r="B37" s="0">
-        <v>81.468000000000004</v>
+        <v>81.470200000000006</v>
       </c>
       <c r="C37" s="0">
-        <v>2.4559000000000002</v>
+        <v>2.4161000000000001</v>
       </c>
       <c r="D37" s="0">
         <v>81.470100000000002</v>
@@ -29425,10 +29425,10 @@
         <v>37</v>
       </c>
       <c r="B38" s="0">
-        <v>81.250399999999999</v>
+        <v>81.253900000000002</v>
       </c>
       <c r="C38" s="0">
-        <v>2.3904000000000001</v>
+        <v>2.1211000000000002</v>
       </c>
       <c r="D38" s="0">
         <v>81.252099999999999</v>
@@ -30182,10 +30182,10 @@
         <v>38</v>
       </c>
       <c r="B39" s="0">
-        <v>81.003600000000006</v>
+        <v>81.004599999999996</v>
       </c>
       <c r="C39" s="0">
-        <v>1.1680999999999999</v>
+        <v>1.1457999999999999</v>
       </c>
       <c r="D39" s="0">
         <v>81.004599999999996</v>
@@ -30939,10 +30939,10 @@
         <v>39</v>
       </c>
       <c r="B40" s="0">
-        <v>81.076899999999995</v>
+        <v>81.041799999999995</v>
       </c>
       <c r="C40" s="0">
-        <v>0.00080000000000000004</v>
+        <v>0</v>
       </c>
       <c r="D40" s="0">
         <v>81.006399999999999</v>
@@ -31696,10 +31696,10 @@
         <v>40</v>
       </c>
       <c r="B41" s="0">
-        <v>81.004900000000006</v>
+        <v>81.006299999999996</v>
       </c>
       <c r="C41" s="0">
-        <v>0.48230000000000001</v>
+        <v>0.22919999999999999</v>
       </c>
       <c r="D41" s="0">
         <v>81.041799999999995</v>
@@ -32453,10 +32453,10 @@
         <v>41</v>
       </c>
       <c r="B42" s="0">
-        <v>81.223500000000001</v>
+        <v>81.259100000000004</v>
       </c>
       <c r="C42" s="0">
-        <v>0.7177</v>
+        <v>0.70730000000000004</v>
       </c>
       <c r="D42" s="0">
         <v>81.224000000000004</v>
@@ -33210,10 +33210,10 @@
         <v>42</v>
       </c>
       <c r="B43" s="0">
-        <v>81.475200000000001</v>
+        <v>81.441100000000006</v>
       </c>
       <c r="C43" s="0">
-        <v>0.98640000000000005</v>
+        <v>0.96289999999999998</v>
       </c>
       <c r="D43" s="0">
         <v>81.476600000000005</v>
@@ -33967,10 +33967,10 @@
         <v>43</v>
       </c>
       <c r="B44" s="0">
-        <v>81.472399999999993</v>
+        <v>81.474000000000004</v>
       </c>
       <c r="C44" s="0">
-        <v>1.9423999999999999</v>
+        <v>1.6918</v>
       </c>
       <c r="D44" s="0">
         <v>81.472899999999996</v>
@@ -34724,10 +34724,10 @@
         <v>44</v>
       </c>
       <c r="B45" s="0">
-        <v>81.178299999999993</v>
+        <v>81.213899999999995</v>
       </c>
       <c r="C45" s="0">
-        <v>2.8012999999999999</v>
+        <v>2.8155999999999999</v>
       </c>
       <c r="D45" s="0">
         <v>81.185699999999997</v>
@@ -35481,10 +35481,10 @@
         <v>45</v>
       </c>
       <c r="B46" s="0">
-        <v>80.960999999999999</v>
+        <v>80.959100000000007</v>
       </c>
       <c r="C46" s="0">
-        <v>2.734</v>
+        <v>2.9649000000000001</v>
       </c>
       <c r="D46" s="0">
         <v>80.960499999999996</v>
@@ -36238,7 +36238,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="0">
-        <v>80.845399999999998</v>
+        <v>80.845500000000001</v>
       </c>
       <c r="C47" s="0">
         <v>3.1547999999999998</v>
@@ -36995,10 +36995,10 @@
         <v>47</v>
       </c>
       <c r="B48" s="0">
-        <v>80.819199999999995</v>
+        <v>80.852199999999996</v>
       </c>
       <c r="C48" s="0">
-        <v>2.0063</v>
+        <v>2.2545999999999999</v>
       </c>
       <c r="D48" s="0">
         <v>80.818399999999997</v>
@@ -37752,10 +37752,10 @@
         <v>48</v>
       </c>
       <c r="B49" s="0">
-        <v>80.971500000000006</v>
+        <v>80.935599999999994</v>
       </c>
       <c r="C49" s="0">
-        <v>-0.0071999999999999998</v>
+        <v>0</v>
       </c>
       <c r="D49" s="0">
         <v>80.971100000000007</v>
@@ -38509,10 +38509,10 @@
         <v>49</v>
       </c>
       <c r="B50" s="0">
-        <v>81.113699999999994</v>
+        <v>81.1126</v>
       </c>
       <c r="C50" s="0">
-        <v>0.2172</v>
+        <v>0</v>
       </c>
       <c r="D50" s="0">
         <v>81.112700000000004</v>
@@ -39266,10 +39266,10 @@
         <v>50</v>
       </c>
       <c r="B51" s="0">
-        <v>81.260300000000001</v>
+        <v>81.257900000000006</v>
       </c>
       <c r="C51" s="0">
-        <v>0.92320000000000002</v>
+        <v>1.1788000000000001</v>
       </c>
       <c r="D51" s="0">
         <v>81.259200000000007</v>
@@ -40023,10 +40023,10 @@
         <v>51</v>
       </c>
       <c r="B52" s="0">
-        <v>81.403599999999997</v>
+        <v>81.403199999999998</v>
       </c>
       <c r="C52" s="0">
-        <v>1.8962000000000001</v>
+        <v>1.6776</v>
       </c>
       <c r="D52" s="0">
         <v>81.368799999999993</v>
@@ -40780,10 +40780,10 @@
         <v>52</v>
       </c>
       <c r="B53" s="0">
-        <v>81.330399999999997</v>
+        <v>81.325900000000004</v>
       </c>
       <c r="C53" s="0">
-        <v>1.8452</v>
+        <v>1.9012</v>
       </c>
       <c r="D53" s="0">
         <v>81.366699999999994</v>
@@ -41537,10 +41537,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="0">
-        <v>81.400999999999996</v>
+        <v>81.400800000000004</v>
       </c>
       <c r="C54" s="0">
-        <v>2.1537999999999999</v>
+        <v>2.1566000000000001</v>
       </c>
       <c r="D54" s="0">
         <v>81.400999999999996</v>
@@ -42294,10 +42294,10 @@
         <v>54</v>
       </c>
       <c r="B55" s="0">
-        <v>81.509299999999996</v>
+        <v>81.509500000000003</v>
       </c>
       <c r="C55" s="0">
-        <v>1.698</v>
+        <v>1.6990000000000001</v>
       </c>
       <c r="D55" s="0">
         <v>81.475099999999998</v>
@@ -43051,10 +43051,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="0">
-        <v>81.289199999999994</v>
+        <v>81.694900000000004</v>
       </c>
       <c r="C56" s="0">
-        <v>11.8696</v>
+        <v>0.74409999999999998</v>
       </c>
       <c r="D56" s="0">
         <v>81.688599999999994</v>
@@ -43808,10 +43808,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="0">
-        <v>81.691699999999997</v>
+        <v>81.690700000000007</v>
       </c>
       <c r="C57" s="0">
-        <v>1.7347999999999999</v>
+        <v>1.9835</v>
       </c>
       <c r="D57" s="0">
         <v>81.691800000000001</v>
@@ -44565,7 +44565,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="0">
-        <v>81.655100000000004</v>
+        <v>81.655299999999997</v>
       </c>
       <c r="C58" s="0">
         <v>1.9749000000000001</v>
@@ -45322,10 +45322,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="0">
-        <v>81.652500000000003</v>
+        <v>81.653999999999996</v>
       </c>
       <c r="C59" s="0">
-        <v>2.4681000000000002</v>
+        <v>2.2216</v>
       </c>
       <c r="D59" s="0">
         <v>81.652500000000003</v>
@@ -46079,10 +46079,10 @@
         <v>59</v>
       </c>
       <c r="B60" s="0">
-        <v>81.719999999999999</v>
+        <v>81.718000000000004</v>
       </c>
       <c r="C60" s="0">
-        <v>2.9836999999999998</v>
+        <v>3.2349999999999999</v>
       </c>
       <c r="D60" s="0">
         <v>81.719999999999999</v>
@@ -46836,10 +46836,10 @@
         <v>60</v>
       </c>
       <c r="B61" s="0">
-        <v>81.652199999999993</v>
+        <v>81.650899999999993</v>
       </c>
       <c r="C61" s="0">
-        <v>2.468</v>
+        <v>2.7145999999999999</v>
       </c>
       <c r="D61" s="0">
         <v>81.652199999999993</v>
@@ -47593,10 +47593,10 @@
         <v>61</v>
       </c>
       <c r="B62" s="0">
-        <v>81.315899999999999</v>
+        <v>81.351600000000005</v>
       </c>
       <c r="C62" s="0">
-        <v>3.3254000000000001</v>
+        <v>3.3384999999999998</v>
       </c>
       <c r="D62" s="0">
         <v>81.315899999999999</v>
@@ -48350,10 +48350,10 @@
         <v>62</v>
       </c>
       <c r="B63" s="0">
-        <v>80.984499999999997</v>
+        <v>80.912899999999993</v>
       </c>
       <c r="C63" s="0">
-        <v>3.8126000000000002</v>
+        <v>4.0856000000000003</v>
       </c>
       <c r="D63" s="0">
         <v>80.984499999999997</v>
@@ -49107,10 +49107,10 @@
         <v>63</v>
       </c>
       <c r="B64" s="0">
-        <v>80.688199999999995</v>
+        <v>80.619200000000006</v>
       </c>
       <c r="C64" s="0">
-        <v>4.2954999999999997</v>
+        <v>3.9603000000000002</v>
       </c>
       <c r="D64" s="0">
         <v>80.688199999999995</v>
@@ -49864,10 +49864,10 @@
         <v>64</v>
       </c>
       <c r="B65" s="0">
-        <v>80.391800000000003</v>
+        <v>80.249600000000001</v>
       </c>
       <c r="C65" s="0">
-        <v>4.7782999999999998</v>
+        <v>4.2363999999999997</v>
       </c>
       <c r="D65" s="0">
         <v>80.391800000000003</v>
@@ -50627,7 +50627,7 @@
   <cols>
     <col min="1" max="1" width="74.5703125" customWidth="true"/>
     <col min="2" max="2" width="6" customWidth="true"/>
-    <col min="3" max="3" width="83.85546875" customWidth="true"/>
+    <col min="3" max="3" width="75.5703125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
